--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
   <si>
     <t>word</t>
   </si>
@@ -152,6 +152,51 @@
   </si>
   <si>
     <t>آچیق قاپو</t>
+  </si>
+  <si>
+    <t>آبدست</t>
+  </si>
+  <si>
+    <t>омовение</t>
+  </si>
+  <si>
+    <t>abdest абдест</t>
+  </si>
+  <si>
+    <t>آبدست اتمك</t>
+  </si>
+  <si>
+    <t>делать</t>
+  </si>
+  <si>
+    <t>etmek этмек</t>
+  </si>
+  <si>
+    <t>اتمك</t>
+  </si>
+  <si>
+    <t>Глагол</t>
+  </si>
+  <si>
+    <t>اوت</t>
+  </si>
+  <si>
+    <t>да</t>
+  </si>
+  <si>
+    <t>evet эвет</t>
+  </si>
+  <si>
+    <t>Частица</t>
+  </si>
+  <si>
+    <t>يوق</t>
+  </si>
+  <si>
+    <t>нет</t>
+  </si>
+  <si>
+    <t>yoq йокъ</t>
   </si>
 </sst>
 </file>
@@ -619,6 +664,71 @@
         <v>9</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="62">
   <si>
     <t>word</t>
   </si>
@@ -166,13 +166,13 @@
     <t>آبدست اتمك</t>
   </si>
   <si>
+    <t>اتمك</t>
+  </si>
+  <si>
     <t>делать</t>
   </si>
   <si>
     <t>etmek этмек</t>
-  </si>
-  <si>
-    <t>اتمك</t>
   </si>
   <si>
     <t>Глагол</t>
@@ -682,14 +682,17 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="B13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>54</v>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="108">
   <si>
     <t>word</t>
   </si>
@@ -76,7 +76,7 @@
     <t>ev эв</t>
   </si>
   <si>
-    <t>بو او</t>
+    <t>او ايشي</t>
   </si>
   <si>
     <t>بو</t>
@@ -197,6 +197,144 @@
   </si>
   <si>
     <t>yoq йокъ</t>
+  </si>
+  <si>
+    <t>آب</t>
+  </si>
+  <si>
+    <t>вода</t>
+  </si>
+  <si>
+    <t>ab аб</t>
+  </si>
+  <si>
+    <t>آب روان</t>
+  </si>
+  <si>
+    <t>عبا</t>
+  </si>
+  <si>
+    <t>грубая шерстяная материя, пальто, риза</t>
+  </si>
+  <si>
+    <t>aba аба</t>
+  </si>
+  <si>
+    <t>بو عبا</t>
+  </si>
+  <si>
+    <t>آباد</t>
+  </si>
+  <si>
+    <t>плодородный</t>
+  </si>
+  <si>
+    <t>abat абат</t>
+  </si>
+  <si>
+    <t>آباد طوپراق</t>
+  </si>
+  <si>
+    <t>آباداني</t>
+  </si>
+  <si>
+    <t>плодородие</t>
+  </si>
+  <si>
+    <t>abadani абадани</t>
+  </si>
+  <si>
+    <t>ايش</t>
+  </si>
+  <si>
+    <t>работа</t>
+  </si>
+  <si>
+    <t>iş иш</t>
+  </si>
+  <si>
+    <t>طوپراق</t>
+  </si>
+  <si>
+    <t>земля</t>
+  </si>
+  <si>
+    <t>topraq топракъ</t>
+  </si>
+  <si>
+    <t>بركتلي طوپراق</t>
+  </si>
+  <si>
+    <t>آبانوس</t>
+  </si>
+  <si>
+    <t>эбеновое дерево</t>
+  </si>
+  <si>
+    <t>abanos абанос</t>
+  </si>
+  <si>
+    <t>آباد آبانوس</t>
+  </si>
+  <si>
+    <t>آباني</t>
+  </si>
+  <si>
+    <t>чалма желтоватого цвета</t>
+  </si>
+  <si>
+    <t>abani абани</t>
+  </si>
+  <si>
+    <t>بو آباني</t>
+  </si>
+  <si>
+    <t>آباقا</t>
+  </si>
+  <si>
+    <t>дядя</t>
+  </si>
+  <si>
+    <t>abaqa абакъа</t>
+  </si>
+  <si>
+    <t>بو آباقا</t>
+  </si>
+  <si>
+    <t>عبد</t>
+  </si>
+  <si>
+    <t>раб, слуга, создание, человек</t>
+  </si>
+  <si>
+    <t>abd абд</t>
+  </si>
+  <si>
+    <t>بو عبد</t>
+  </si>
+  <si>
+    <t>آبدال</t>
+  </si>
+  <si>
+    <t>шалопай, идиот</t>
+  </si>
+  <si>
+    <t>abdal абдал</t>
+  </si>
+  <si>
+    <t>بو آبدال عبد</t>
+  </si>
+  <si>
+    <t>آبداللق</t>
+  </si>
+  <si>
+    <t>глупость</t>
+  </si>
+  <si>
+    <t>abdallıq абдаллыкъ</t>
+  </si>
+  <si>
+    <t>بو آبداللق</t>
   </si>
 </sst>
 </file>
@@ -476,6 +614,10 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="33.13"/>
+    <col customWidth="1" min="3" max="3" width="38.0"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -732,6 +874,210 @@
         <v>58</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="127">
   <si>
     <t>word</t>
   </si>
@@ -28,7 +28,7 @@
     <t>category</t>
   </si>
   <si>
-    <t>كتاب</t>
+    <t>کتاب</t>
   </si>
   <si>
     <t>книга</t>
@@ -94,7 +94,7 @@
     <t>Местоимение</t>
   </si>
   <si>
-    <t>بيلگي</t>
+    <t>بیلگی</t>
   </si>
   <si>
     <t>знание</t>
@@ -163,10 +163,10 @@
     <t>abdest абдест</t>
   </si>
   <si>
-    <t>آبدست اتمك</t>
-  </si>
-  <si>
-    <t>اتمك</t>
+    <t>آبدست اتمک</t>
+  </si>
+  <si>
+    <t>اتمک</t>
   </si>
   <si>
     <t>делать</t>
@@ -277,7 +277,7 @@
     <t>آباد آبانوس</t>
   </si>
   <si>
-    <t>آباني</t>
+    <t>آبانی</t>
   </si>
   <si>
     <t>чалма желтоватого цвета</t>
@@ -335,6 +335,63 @@
   </si>
   <si>
     <t>بو آبداللق</t>
+  </si>
+  <si>
+    <t>بن</t>
+  </si>
+  <si>
+    <t>я</t>
+  </si>
+  <si>
+    <t>ben бен</t>
+  </si>
+  <si>
+    <t>بن عبدم</t>
+  </si>
+  <si>
+    <t>سن</t>
+  </si>
+  <si>
+    <t>ты</t>
+  </si>
+  <si>
+    <t>sen сен</t>
+  </si>
+  <si>
+    <t>سن بنم آباقاسڭ</t>
+  </si>
+  <si>
+    <t>он, она, оно</t>
+  </si>
+  <si>
+    <t>o о</t>
+  </si>
+  <si>
+    <t>او كتابم</t>
+  </si>
+  <si>
+    <t>بلاغت</t>
+  </si>
+  <si>
+    <t>красноречие</t>
+  </si>
+  <si>
+    <t>belâğat белягъат</t>
+  </si>
+  <si>
+    <t>بن لاف بلاغتینی سویم</t>
+  </si>
+  <si>
+    <t>سومک</t>
+  </si>
+  <si>
+    <t>любить</t>
+  </si>
+  <si>
+    <t>sevmek севмек</t>
+  </si>
+  <si>
+    <t>بن سنی سویم</t>
   </si>
 </sst>
 </file>
@@ -834,7 +891,7 @@
         <v>53</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>54</v>
@@ -1076,6 +1133,91 @@
       </c>
       <c r="E27" s="1" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="128">
   <si>
     <t>word</t>
   </si>
@@ -37,7 +37,7 @@
     <t>kitap китап</t>
   </si>
   <si>
-    <t>بو كتاب</t>
+    <t>بو کتاب</t>
   </si>
   <si>
     <t>Существительное</t>
@@ -76,183 +76,186 @@
     <t>ev эв</t>
   </si>
   <si>
+    <t>او ايشی</t>
+  </si>
+  <si>
+    <t>بو</t>
+  </si>
+  <si>
+    <t>это</t>
+  </si>
+  <si>
+    <t>bu бу</t>
+  </si>
+  <si>
+    <t>بو نه؟</t>
+  </si>
+  <si>
+    <t>Местоимение</t>
+  </si>
+  <si>
+    <t>بیلگی</t>
+  </si>
+  <si>
+    <t>знание</t>
+  </si>
+  <si>
+    <t>bilgi бильги</t>
+  </si>
+  <si>
+    <t>بیلگی نورى</t>
+  </si>
+  <si>
+    <t>لغت</t>
+  </si>
+  <si>
+    <t>словарь</t>
+  </si>
+  <si>
+    <t>lüğat люгъат</t>
+  </si>
+  <si>
+    <t>روسجه لغت</t>
+  </si>
+  <si>
+    <t>پنجره</t>
+  </si>
+  <si>
+    <t>окно</t>
+  </si>
+  <si>
+    <t>pencere пенджере</t>
+  </si>
+  <si>
+    <t>آچیق پنجره</t>
+  </si>
+  <si>
+    <t>آچیق</t>
+  </si>
+  <si>
+    <t>открытый</t>
+  </si>
+  <si>
+    <t>açıq ачыкъ</t>
+  </si>
+  <si>
+    <t>Прилагательное</t>
+  </si>
+  <si>
+    <t>قاپو</t>
+  </si>
+  <si>
+    <t>дверь</t>
+  </si>
+  <si>
+    <t>qapu къапу</t>
+  </si>
+  <si>
+    <t>آچیق قاپو</t>
+  </si>
+  <si>
+    <t>آبدست</t>
+  </si>
+  <si>
+    <t>омовение</t>
+  </si>
+  <si>
+    <t>abdest абдест</t>
+  </si>
+  <si>
+    <t>آبدست اتمک</t>
+  </si>
+  <si>
+    <t>اتمک</t>
+  </si>
+  <si>
+    <t>делать</t>
+  </si>
+  <si>
+    <t>etmek этмек</t>
+  </si>
+  <si>
+    <t>Глагол</t>
+  </si>
+  <si>
+    <t>اوت</t>
+  </si>
+  <si>
+    <t>да</t>
+  </si>
+  <si>
+    <t>evet эвет</t>
+  </si>
+  <si>
+    <t>Частица</t>
+  </si>
+  <si>
+    <t>يوق</t>
+  </si>
+  <si>
+    <t>нет</t>
+  </si>
+  <si>
+    <t>yoq йокъ</t>
+  </si>
+  <si>
+    <t>آب</t>
+  </si>
+  <si>
+    <t>вода</t>
+  </si>
+  <si>
+    <t>ab аб</t>
+  </si>
+  <si>
+    <t>آب روان</t>
+  </si>
+  <si>
+    <t>عبا</t>
+  </si>
+  <si>
+    <t>грубая шерстяная материя, пальто, риза</t>
+  </si>
+  <si>
+    <t>aba аба</t>
+  </si>
+  <si>
+    <t>بو عبا</t>
+  </si>
+  <si>
+    <t>آباد</t>
+  </si>
+  <si>
+    <t>плодородный</t>
+  </si>
+  <si>
+    <t>abat абат</t>
+  </si>
+  <si>
+    <t>آباد طوپراق</t>
+  </si>
+  <si>
+    <t>آبادانی</t>
+  </si>
+  <si>
+    <t>плодородие</t>
+  </si>
+  <si>
+    <t>abadani абадани</t>
+  </si>
+  <si>
+    <t>ايش</t>
+  </si>
+  <si>
+    <t>работа</t>
+  </si>
+  <si>
+    <t>iş иш</t>
+  </si>
+  <si>
     <t>او ايشي</t>
   </si>
   <si>
-    <t>بو</t>
-  </si>
-  <si>
-    <t>это</t>
-  </si>
-  <si>
-    <t>bu бу</t>
-  </si>
-  <si>
-    <t>بو نه؟</t>
-  </si>
-  <si>
-    <t>Местоимение</t>
-  </si>
-  <si>
-    <t>بیلگی</t>
-  </si>
-  <si>
-    <t>знание</t>
-  </si>
-  <si>
-    <t>bilgi бильги</t>
-  </si>
-  <si>
-    <t>بيلگى نورى</t>
-  </si>
-  <si>
-    <t>لغت</t>
-  </si>
-  <si>
-    <t>словарь</t>
-  </si>
-  <si>
-    <t>lüğat люгъат</t>
-  </si>
-  <si>
-    <t>روسچه لغت</t>
-  </si>
-  <si>
-    <t>پنجره</t>
-  </si>
-  <si>
-    <t>окно</t>
-  </si>
-  <si>
-    <t>pencere пенджере</t>
-  </si>
-  <si>
-    <t>آچیق پنجره</t>
-  </si>
-  <si>
-    <t>آچیق</t>
-  </si>
-  <si>
-    <t>открытый</t>
-  </si>
-  <si>
-    <t>açıq ачыкъ</t>
-  </si>
-  <si>
-    <t>Прилагательное</t>
-  </si>
-  <si>
-    <t>قاپو</t>
-  </si>
-  <si>
-    <t>дверь</t>
-  </si>
-  <si>
-    <t>qapu къапу</t>
-  </si>
-  <si>
-    <t>آچیق قاپو</t>
-  </si>
-  <si>
-    <t>آبدست</t>
-  </si>
-  <si>
-    <t>омовение</t>
-  </si>
-  <si>
-    <t>abdest абдест</t>
-  </si>
-  <si>
-    <t>آبدست اتمک</t>
-  </si>
-  <si>
-    <t>اتمک</t>
-  </si>
-  <si>
-    <t>делать</t>
-  </si>
-  <si>
-    <t>etmek этмек</t>
-  </si>
-  <si>
-    <t>Глагол</t>
-  </si>
-  <si>
-    <t>اوت</t>
-  </si>
-  <si>
-    <t>да</t>
-  </si>
-  <si>
-    <t>evet эвет</t>
-  </si>
-  <si>
-    <t>Частица</t>
-  </si>
-  <si>
-    <t>يوق</t>
-  </si>
-  <si>
-    <t>нет</t>
-  </si>
-  <si>
-    <t>yoq йокъ</t>
-  </si>
-  <si>
-    <t>آب</t>
-  </si>
-  <si>
-    <t>вода</t>
-  </si>
-  <si>
-    <t>ab аб</t>
-  </si>
-  <si>
-    <t>آب روان</t>
-  </si>
-  <si>
-    <t>عبا</t>
-  </si>
-  <si>
-    <t>грубая шерстяная материя, пальто, риза</t>
-  </si>
-  <si>
-    <t>aba аба</t>
-  </si>
-  <si>
-    <t>بو عبا</t>
-  </si>
-  <si>
-    <t>آباد</t>
-  </si>
-  <si>
-    <t>плодородный</t>
-  </si>
-  <si>
-    <t>abat абат</t>
-  </si>
-  <si>
-    <t>آباد طوپراق</t>
-  </si>
-  <si>
-    <t>آباداني</t>
-  </si>
-  <si>
-    <t>плодородие</t>
-  </si>
-  <si>
-    <t>abadani абадани</t>
-  </si>
-  <si>
-    <t>ايش</t>
-  </si>
-  <si>
-    <t>работа</t>
-  </si>
-  <si>
-    <t>iş иш</t>
-  </si>
-  <si>
     <t>طوپراق</t>
   </si>
   <si>
@@ -262,7 +265,7 @@
     <t>topraq топракъ</t>
   </si>
   <si>
-    <t>بركتلي طوپراق</t>
+    <t>بركتلی طوپراق</t>
   </si>
   <si>
     <t>آبانوس</t>
@@ -286,7 +289,7 @@
     <t>abani абани</t>
   </si>
   <si>
-    <t>بو آباني</t>
+    <t>بو آبانی</t>
   </si>
   <si>
     <t>آباقا</t>
@@ -367,7 +370,7 @@
     <t>o о</t>
   </si>
   <si>
-    <t>او كتابم</t>
+    <t>او کتابم</t>
   </si>
   <si>
     <t>بلاغت</t>
@@ -1010,7 +1013,7 @@
         <v>79</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>9</v>
@@ -1018,16 +1021,16 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>9</v>
@@ -1035,16 +1038,16 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>9</v>
@@ -1052,16 +1055,16 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>9</v>
@@ -1069,16 +1072,16 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>9</v>
@@ -1086,16 +1089,16 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>9</v>
@@ -1103,16 +1106,16 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>42</v>
@@ -1120,16 +1123,16 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>9</v>
@@ -1137,16 +1140,16 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>26</v>
@@ -1154,16 +1157,16 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>26</v>
@@ -1174,13 +1177,13 @@
         <v>18</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>26</v>
@@ -1188,16 +1191,16 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>9</v>
@@ -1205,16 +1208,16 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>54</v>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -76,7 +76,7 @@
     <t>ev эв</t>
   </si>
   <si>
-    <t>او ايشی</t>
+    <t>او ایشی</t>
   </si>
   <si>
     <t>بو</t>
@@ -103,7 +103,7 @@
     <t>bilgi бильги</t>
   </si>
   <si>
-    <t>بیلگی نورى</t>
+    <t>بیلگی نوری</t>
   </si>
   <si>
     <t>لغت</t>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="158">
   <si>
     <t>word</t>
   </si>
@@ -395,6 +395,96 @@
   </si>
   <si>
     <t>بن سنی سویم</t>
+  </si>
+  <si>
+    <t>مقام</t>
+  </si>
+  <si>
+    <t>место</t>
+  </si>
+  <si>
+    <t>maqam макъам</t>
+  </si>
+  <si>
+    <t>برکتلی مقام</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> برکت</t>
+  </si>
+  <si>
+    <t>благословение</t>
+  </si>
+  <si>
+    <t>bereket берекет</t>
+  </si>
+  <si>
+    <t>برکت اتسڭ</t>
+  </si>
+  <si>
+    <t>برکتلی</t>
+  </si>
+  <si>
+    <t>благословенный</t>
+  </si>
+  <si>
+    <t>bereketli берекетли</t>
+  </si>
+  <si>
+    <t>برکتلی آدم</t>
+  </si>
+  <si>
+    <t>آدم</t>
+  </si>
+  <si>
+    <t>Адам (первый человек), человек</t>
+  </si>
+  <si>
+    <t>adam адам</t>
+  </si>
+  <si>
+    <t>بو آدم</t>
+  </si>
+  <si>
+    <t>مکان</t>
+  </si>
+  <si>
+    <t>mekân мекян</t>
+  </si>
+  <si>
+    <t>مکانسز</t>
+  </si>
+  <si>
+    <t>بز</t>
+  </si>
+  <si>
+    <t>мы</t>
+  </si>
+  <si>
+    <t>biz биз</t>
+  </si>
+  <si>
+    <t>سز</t>
+  </si>
+  <si>
+    <t>вы</t>
+  </si>
+  <si>
+    <t>siz сиз</t>
+  </si>
+  <si>
+    <t>اولر</t>
+  </si>
+  <si>
+    <t>они</t>
+  </si>
+  <si>
+    <t>olar олар</t>
+  </si>
+  <si>
+    <t>без, не</t>
+  </si>
+  <si>
+    <t>Предлог</t>
   </si>
 </sst>
 </file>
@@ -1223,6 +1313,147 @@
         <v>54</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="194">
   <si>
     <t>word</t>
   </si>
@@ -28,6 +28,507 @@
     <t>category</t>
   </si>
   <si>
+    <t>آب</t>
+  </si>
+  <si>
+    <t>вода</t>
+  </si>
+  <si>
+    <t>ab аб</t>
+  </si>
+  <si>
+    <t>آب روان</t>
+  </si>
+  <si>
+    <t>Существительное</t>
+  </si>
+  <si>
+    <t>آباد</t>
+  </si>
+  <si>
+    <t>плодородный</t>
+  </si>
+  <si>
+    <t>abat абат</t>
+  </si>
+  <si>
+    <t>آباد طوپراق</t>
+  </si>
+  <si>
+    <t>Прилагательное</t>
+  </si>
+  <si>
+    <t>آبادانی</t>
+  </si>
+  <si>
+    <t>плодородие</t>
+  </si>
+  <si>
+    <t>abadani абадани</t>
+  </si>
+  <si>
+    <t>آباقا</t>
+  </si>
+  <si>
+    <t>дядя</t>
+  </si>
+  <si>
+    <t>abaqa абакъа</t>
+  </si>
+  <si>
+    <t>بو آباقا</t>
+  </si>
+  <si>
+    <t>آبانوس</t>
+  </si>
+  <si>
+    <t>эбеновое дерево</t>
+  </si>
+  <si>
+    <t>abanos абанос</t>
+  </si>
+  <si>
+    <t>آباد آبانوس</t>
+  </si>
+  <si>
+    <t>آبانی</t>
+  </si>
+  <si>
+    <t>чалма желтоватого цвета</t>
+  </si>
+  <si>
+    <t>abani абани</t>
+  </si>
+  <si>
+    <t>بو آبانی</t>
+  </si>
+  <si>
+    <t>آبدال</t>
+  </si>
+  <si>
+    <t>шалопай, идиот</t>
+  </si>
+  <si>
+    <t>abdal абдал</t>
+  </si>
+  <si>
+    <t>بو آبدال عبد</t>
+  </si>
+  <si>
+    <t>آبداللق</t>
+  </si>
+  <si>
+    <t>глупость</t>
+  </si>
+  <si>
+    <t>abdallıq абдаллыкъ</t>
+  </si>
+  <si>
+    <t>بو آبداللق</t>
+  </si>
+  <si>
+    <t>آبدست</t>
+  </si>
+  <si>
+    <t>омовение</t>
+  </si>
+  <si>
+    <t>abdest абдест</t>
+  </si>
+  <si>
+    <t>آبدست اتمک</t>
+  </si>
+  <si>
+    <t>آچیق</t>
+  </si>
+  <si>
+    <t>открытый</t>
+  </si>
+  <si>
+    <t>açıq ачыкъ</t>
+  </si>
+  <si>
+    <t>آچیق پنجره</t>
+  </si>
+  <si>
+    <t>آدم</t>
+  </si>
+  <si>
+    <t>Адам (первый человек, имя), человек</t>
+  </si>
+  <si>
+    <t>adam адам</t>
+  </si>
+  <si>
+    <t>بو آدم</t>
+  </si>
+  <si>
+    <t>اتمک</t>
+  </si>
+  <si>
+    <t>делать</t>
+  </si>
+  <si>
+    <t>etmek этмек</t>
+  </si>
+  <si>
+    <t>Глагол</t>
+  </si>
+  <si>
+    <t>اسم</t>
+  </si>
+  <si>
+    <t>имя (существительное)</t>
+  </si>
+  <si>
+    <t>isim исим</t>
+  </si>
+  <si>
+    <t>اعجمی</t>
+  </si>
+  <si>
+    <t>перс, чужестранец, иностранец</t>
+  </si>
+  <si>
+    <t>acemi аджеми</t>
+  </si>
+  <si>
+    <t>بو اعجمی</t>
+  </si>
+  <si>
+    <t>او</t>
+  </si>
+  <si>
+    <t>дом</t>
+  </si>
+  <si>
+    <t>ev эв</t>
+  </si>
+  <si>
+    <t>او ایشی</t>
+  </si>
+  <si>
+    <t>он, она, оно</t>
+  </si>
+  <si>
+    <t>o о</t>
+  </si>
+  <si>
+    <t>او کتابم</t>
+  </si>
+  <si>
+    <t>Местоимение</t>
+  </si>
+  <si>
+    <t>اوت</t>
+  </si>
+  <si>
+    <t>да</t>
+  </si>
+  <si>
+    <t>evet эвет</t>
+  </si>
+  <si>
+    <t>Частица</t>
+  </si>
+  <si>
+    <t>اولر</t>
+  </si>
+  <si>
+    <t>они</t>
+  </si>
+  <si>
+    <t>olar олар</t>
+  </si>
+  <si>
+    <t>اولر برکتلی آدم</t>
+  </si>
+  <si>
+    <t>ايش</t>
+  </si>
+  <si>
+    <t>работа</t>
+  </si>
+  <si>
+    <t>iş иш</t>
+  </si>
+  <si>
+    <t>او ايشي</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> برکت</t>
+  </si>
+  <si>
+    <t>благословение</t>
+  </si>
+  <si>
+    <t>bereket берекет</t>
+  </si>
+  <si>
+    <t>برکت اتسڭ</t>
+  </si>
+  <si>
+    <t>برکتلی</t>
+  </si>
+  <si>
+    <t>благословенный</t>
+  </si>
+  <si>
+    <t>bereketli берекетли</t>
+  </si>
+  <si>
+    <t>برکتلی آدم</t>
+  </si>
+  <si>
+    <t>بز</t>
+  </si>
+  <si>
+    <t>мы</t>
+  </si>
+  <si>
+    <t>biz биз</t>
+  </si>
+  <si>
+    <t>بزم دینمز اسلام</t>
+  </si>
+  <si>
+    <t>بغل</t>
+  </si>
+  <si>
+    <t>мул, лошак</t>
+  </si>
+  <si>
+    <t>bağl багъль</t>
+  </si>
+  <si>
+    <t>بو بغل</t>
+  </si>
+  <si>
+    <t>بلاغت</t>
+  </si>
+  <si>
+    <t>красноречие</t>
+  </si>
+  <si>
+    <t>belâğat белягъат</t>
+  </si>
+  <si>
+    <t>بن لاف بلاغتینی سویم</t>
+  </si>
+  <si>
+    <t>بن</t>
+  </si>
+  <si>
+    <t>я</t>
+  </si>
+  <si>
+    <t>ben бен</t>
+  </si>
+  <si>
+    <t>بن عبدم</t>
+  </si>
+  <si>
+    <t>بو</t>
+  </si>
+  <si>
+    <t>это</t>
+  </si>
+  <si>
+    <t>bu бу</t>
+  </si>
+  <si>
+    <t>بو نه؟</t>
+  </si>
+  <si>
+    <t>بیلگی</t>
+  </si>
+  <si>
+    <t>знание</t>
+  </si>
+  <si>
+    <t>bilgi бильги</t>
+  </si>
+  <si>
+    <t>بیلگی نوری</t>
+  </si>
+  <si>
+    <t>پنجره</t>
+  </si>
+  <si>
+    <t>окно</t>
+  </si>
+  <si>
+    <t>pencere пенджере</t>
+  </si>
+  <si>
+    <t>ستان</t>
+  </si>
+  <si>
+    <t>страна</t>
+  </si>
+  <si>
+    <t>stan стан</t>
+  </si>
+  <si>
+    <t>بو بنم ستانم</t>
+  </si>
+  <si>
+    <t>سز</t>
+  </si>
+  <si>
+    <t>вы</t>
+  </si>
+  <si>
+    <t>siz сиз</t>
+  </si>
+  <si>
+    <t>سز نه یاپاسڭز</t>
+  </si>
+  <si>
+    <t>без, не</t>
+  </si>
+  <si>
+    <t>برکتسز</t>
+  </si>
+  <si>
+    <t>Предлог</t>
+  </si>
+  <si>
+    <t>سن</t>
+  </si>
+  <si>
+    <t>ты</t>
+  </si>
+  <si>
+    <t>sen сен</t>
+  </si>
+  <si>
+    <t>سن بنم آباقاسڭ</t>
+  </si>
+  <si>
+    <t>سومک</t>
+  </si>
+  <si>
+    <t>любить</t>
+  </si>
+  <si>
+    <t>sevmek севмек</t>
+  </si>
+  <si>
+    <t>بن سنی سویم</t>
+  </si>
+  <si>
+    <t>صفت</t>
+  </si>
+  <si>
+    <t>описание, прилагательное</t>
+  </si>
+  <si>
+    <t>sıfat сыфат</t>
+  </si>
+  <si>
+    <t>طوپراق</t>
+  </si>
+  <si>
+    <t>земля</t>
+  </si>
+  <si>
+    <t>topraq топракъ</t>
+  </si>
+  <si>
+    <t>بركتلی طوپراق</t>
+  </si>
+  <si>
+    <t>عبا</t>
+  </si>
+  <si>
+    <t>грубая шерстяная материя, пальто, риза</t>
+  </si>
+  <si>
+    <t>aba аба</t>
+  </si>
+  <si>
+    <t>بو عبا</t>
+  </si>
+  <si>
+    <t>عبد</t>
+  </si>
+  <si>
+    <t>раб, слуга, создание, человек</t>
+  </si>
+  <si>
+    <t>abd абд</t>
+  </si>
+  <si>
+    <t>بو عبد</t>
+  </si>
+  <si>
+    <t>عجم</t>
+  </si>
+  <si>
+    <t>acem аджем</t>
+  </si>
+  <si>
+    <t>بو عجم</t>
+  </si>
+  <si>
+    <t>عجمستان</t>
+  </si>
+  <si>
+    <t>Персия</t>
+  </si>
+  <si>
+    <t>acemistan аджемистан</t>
+  </si>
+  <si>
+    <t>بو عجمستان</t>
+  </si>
+  <si>
+    <t>فعل</t>
+  </si>
+  <si>
+    <t>действие, глагол</t>
+  </si>
+  <si>
+    <t>fiil фииль</t>
+  </si>
+  <si>
+    <t>فیل</t>
+  </si>
+  <si>
+    <t>слон</t>
+  </si>
+  <si>
+    <t>fil филь</t>
+  </si>
+  <si>
+    <t>بو بالابان فیل</t>
+  </si>
+  <si>
+    <t>قاپو</t>
+  </si>
+  <si>
+    <t>дверь</t>
+  </si>
+  <si>
+    <t>qapu къапу</t>
+  </si>
+  <si>
+    <t>آچیق قاپو</t>
+  </si>
+  <si>
+    <t>قلم</t>
+  </si>
+  <si>
+    <t>ручка</t>
+  </si>
+  <si>
+    <t>qalem къалем</t>
+  </si>
+  <si>
+    <t>بو قلم</t>
+  </si>
+  <si>
     <t>کتاب</t>
   </si>
   <si>
@@ -40,19 +541,16 @@
     <t>بو کتاب</t>
   </si>
   <si>
-    <t>Существительное</t>
-  </si>
-  <si>
-    <t>قلم</t>
-  </si>
-  <si>
-    <t>ручка</t>
-  </si>
-  <si>
-    <t>qalem къалем</t>
-  </si>
-  <si>
-    <t>بو قلم</t>
+    <t>لغت</t>
+  </si>
+  <si>
+    <t>словарь</t>
+  </si>
+  <si>
+    <t>lüğat люгъат</t>
+  </si>
+  <si>
+    <t>روسجه لغت</t>
   </si>
   <si>
     <t>مدرسة</t>
@@ -67,127 +565,25 @@
     <t>بو مدرسة</t>
   </si>
   <si>
-    <t>او</t>
-  </si>
-  <si>
-    <t>дом</t>
-  </si>
-  <si>
-    <t>ev эв</t>
-  </si>
-  <si>
-    <t>او ایشی</t>
-  </si>
-  <si>
-    <t>بو</t>
-  </si>
-  <si>
-    <t>это</t>
-  </si>
-  <si>
-    <t>bu бу</t>
-  </si>
-  <si>
-    <t>بو نه؟</t>
-  </si>
-  <si>
-    <t>Местоимение</t>
-  </si>
-  <si>
-    <t>بیلگی</t>
-  </si>
-  <si>
-    <t>знание</t>
-  </si>
-  <si>
-    <t>bilgi бильги</t>
-  </si>
-  <si>
-    <t>بیلگی نوری</t>
-  </si>
-  <si>
-    <t>لغت</t>
-  </si>
-  <si>
-    <t>словарь</t>
-  </si>
-  <si>
-    <t>lüğat люгъат</t>
-  </si>
-  <si>
-    <t>روسجه لغت</t>
-  </si>
-  <si>
-    <t>پنجره</t>
-  </si>
-  <si>
-    <t>окно</t>
-  </si>
-  <si>
-    <t>pencere пенджере</t>
-  </si>
-  <si>
-    <t>آچیق پنجره</t>
-  </si>
-  <si>
-    <t>آچیق</t>
-  </si>
-  <si>
-    <t>открытый</t>
-  </si>
-  <si>
-    <t>açıq ачыкъ</t>
-  </si>
-  <si>
-    <t>Прилагательное</t>
-  </si>
-  <si>
-    <t>قاپو</t>
-  </si>
-  <si>
-    <t>дверь</t>
-  </si>
-  <si>
-    <t>qapu къапу</t>
-  </si>
-  <si>
-    <t>آچیق قاپو</t>
-  </si>
-  <si>
-    <t>آبدست</t>
-  </si>
-  <si>
-    <t>омовение</t>
-  </si>
-  <si>
-    <t>abdest абдест</t>
-  </si>
-  <si>
-    <t>آبدست اتمک</t>
-  </si>
-  <si>
-    <t>اتمک</t>
-  </si>
-  <si>
-    <t>делать</t>
-  </si>
-  <si>
-    <t>etmek этмек</t>
-  </si>
-  <si>
-    <t>Глагол</t>
-  </si>
-  <si>
-    <t>اوت</t>
-  </si>
-  <si>
-    <t>да</t>
-  </si>
-  <si>
-    <t>evet эвет</t>
-  </si>
-  <si>
-    <t>Частица</t>
+    <t>مقام</t>
+  </si>
+  <si>
+    <t>место</t>
+  </si>
+  <si>
+    <t>maqam макъам</t>
+  </si>
+  <si>
+    <t>برکتلی مقام</t>
+  </si>
+  <si>
+    <t>مکان</t>
+  </si>
+  <si>
+    <t>mekân мекян</t>
+  </si>
+  <si>
+    <t>مکانسز</t>
   </si>
   <si>
     <t>يوق</t>
@@ -197,294 +593,6 @@
   </si>
   <si>
     <t>yoq йокъ</t>
-  </si>
-  <si>
-    <t>آب</t>
-  </si>
-  <si>
-    <t>вода</t>
-  </si>
-  <si>
-    <t>ab аб</t>
-  </si>
-  <si>
-    <t>آب روان</t>
-  </si>
-  <si>
-    <t>عبا</t>
-  </si>
-  <si>
-    <t>грубая шерстяная материя, пальто, риза</t>
-  </si>
-  <si>
-    <t>aba аба</t>
-  </si>
-  <si>
-    <t>بو عبا</t>
-  </si>
-  <si>
-    <t>آباد</t>
-  </si>
-  <si>
-    <t>плодородный</t>
-  </si>
-  <si>
-    <t>abat абат</t>
-  </si>
-  <si>
-    <t>آباد طوپراق</t>
-  </si>
-  <si>
-    <t>آبادانی</t>
-  </si>
-  <si>
-    <t>плодородие</t>
-  </si>
-  <si>
-    <t>abadani абадани</t>
-  </si>
-  <si>
-    <t>ايش</t>
-  </si>
-  <si>
-    <t>работа</t>
-  </si>
-  <si>
-    <t>iş иш</t>
-  </si>
-  <si>
-    <t>او ايشي</t>
-  </si>
-  <si>
-    <t>طوپراق</t>
-  </si>
-  <si>
-    <t>земля</t>
-  </si>
-  <si>
-    <t>topraq топракъ</t>
-  </si>
-  <si>
-    <t>بركتلی طوپراق</t>
-  </si>
-  <si>
-    <t>آبانوس</t>
-  </si>
-  <si>
-    <t>эбеновое дерево</t>
-  </si>
-  <si>
-    <t>abanos абанос</t>
-  </si>
-  <si>
-    <t>آباد آبانوس</t>
-  </si>
-  <si>
-    <t>آبانی</t>
-  </si>
-  <si>
-    <t>чалма желтоватого цвета</t>
-  </si>
-  <si>
-    <t>abani абани</t>
-  </si>
-  <si>
-    <t>بو آبانی</t>
-  </si>
-  <si>
-    <t>آباقا</t>
-  </si>
-  <si>
-    <t>дядя</t>
-  </si>
-  <si>
-    <t>abaqa абакъа</t>
-  </si>
-  <si>
-    <t>بو آباقا</t>
-  </si>
-  <si>
-    <t>عبد</t>
-  </si>
-  <si>
-    <t>раб, слуга, создание, человек</t>
-  </si>
-  <si>
-    <t>abd абд</t>
-  </si>
-  <si>
-    <t>بو عبد</t>
-  </si>
-  <si>
-    <t>آبدال</t>
-  </si>
-  <si>
-    <t>шалопай, идиот</t>
-  </si>
-  <si>
-    <t>abdal абдал</t>
-  </si>
-  <si>
-    <t>بو آبدال عبد</t>
-  </si>
-  <si>
-    <t>آبداللق</t>
-  </si>
-  <si>
-    <t>глупость</t>
-  </si>
-  <si>
-    <t>abdallıq абдаллыкъ</t>
-  </si>
-  <si>
-    <t>بو آبداللق</t>
-  </si>
-  <si>
-    <t>بن</t>
-  </si>
-  <si>
-    <t>я</t>
-  </si>
-  <si>
-    <t>ben бен</t>
-  </si>
-  <si>
-    <t>بن عبدم</t>
-  </si>
-  <si>
-    <t>سن</t>
-  </si>
-  <si>
-    <t>ты</t>
-  </si>
-  <si>
-    <t>sen сен</t>
-  </si>
-  <si>
-    <t>سن بنم آباقاسڭ</t>
-  </si>
-  <si>
-    <t>он, она, оно</t>
-  </si>
-  <si>
-    <t>o о</t>
-  </si>
-  <si>
-    <t>او کتابم</t>
-  </si>
-  <si>
-    <t>بلاغت</t>
-  </si>
-  <si>
-    <t>красноречие</t>
-  </si>
-  <si>
-    <t>belâğat белягъат</t>
-  </si>
-  <si>
-    <t>بن لاف بلاغتینی سویم</t>
-  </si>
-  <si>
-    <t>سومک</t>
-  </si>
-  <si>
-    <t>любить</t>
-  </si>
-  <si>
-    <t>sevmek севмек</t>
-  </si>
-  <si>
-    <t>بن سنی سویم</t>
-  </si>
-  <si>
-    <t>مقام</t>
-  </si>
-  <si>
-    <t>место</t>
-  </si>
-  <si>
-    <t>maqam макъам</t>
-  </si>
-  <si>
-    <t>برکتلی مقام</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> برکت</t>
-  </si>
-  <si>
-    <t>благословение</t>
-  </si>
-  <si>
-    <t>bereket берекет</t>
-  </si>
-  <si>
-    <t>برکت اتسڭ</t>
-  </si>
-  <si>
-    <t>برکتلی</t>
-  </si>
-  <si>
-    <t>благословенный</t>
-  </si>
-  <si>
-    <t>bereketli берекетли</t>
-  </si>
-  <si>
-    <t>برکتلی آدم</t>
-  </si>
-  <si>
-    <t>آدم</t>
-  </si>
-  <si>
-    <t>Адам (первый человек), человек</t>
-  </si>
-  <si>
-    <t>adam адам</t>
-  </si>
-  <si>
-    <t>بو آدم</t>
-  </si>
-  <si>
-    <t>مکان</t>
-  </si>
-  <si>
-    <t>mekân мекян</t>
-  </si>
-  <si>
-    <t>مکانسز</t>
-  </si>
-  <si>
-    <t>بز</t>
-  </si>
-  <si>
-    <t>мы</t>
-  </si>
-  <si>
-    <t>biz биз</t>
-  </si>
-  <si>
-    <t>سز</t>
-  </si>
-  <si>
-    <t>вы</t>
-  </si>
-  <si>
-    <t>siz сиз</t>
-  </si>
-  <si>
-    <t>اولر</t>
-  </si>
-  <si>
-    <t>они</t>
-  </si>
-  <si>
-    <t>olar олар</t>
-  </si>
-  <si>
-    <t>без, не</t>
-  </si>
-  <si>
-    <t>Предлог</t>
   </si>
 </sst>
 </file>
@@ -539,13 +647,13 @@
     <xf borderId="0" fillId="2" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -790,21 +898,21 @@
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -813,32 +921,32 @@
       <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>14</v>
+      <c r="A4" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -847,7 +955,7 @@
       <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -855,7 +963,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -864,236 +972,236 @@
       <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="s">
+      <c r="B8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="s">
+      <c r="B10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="E10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="s">
+      <c r="B11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="s">
+      <c r="B12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="s">
+      <c r="B13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="1" t="s">
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="s">
+      <c r="B14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="s">
+      <c r="C15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="D15" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="E15" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="s">
+      <c r="B16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="s">
+      <c r="C17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="D17" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="4" t="s">
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="s">
+      <c r="B18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="4" t="s">
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="s">
+      <c r="B19" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="E19" s="1" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>77</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -1102,7 +1210,7 @@
       <c r="C20" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>80</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -1110,7 +1218,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1119,7 +1227,7 @@
       <c r="C21" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>84</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -1127,7 +1235,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>85</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1136,15 +1244,15 @@
       <c r="C22" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>88</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>89</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -1153,15 +1261,15 @@
       <c r="C23" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>92</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>93</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -1170,7 +1278,7 @@
       <c r="C24" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>96</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -1178,7 +1286,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -1187,7 +1295,7 @@
       <c r="C25" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>100</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -1195,7 +1303,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -1204,15 +1312,15 @@
       <c r="C26" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>104</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>105</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -1225,11 +1333,11 @@
         <v>108</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>109</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -1238,15 +1346,15 @@
       <c r="C28" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>113</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -1255,16 +1363,16 @@
       <c r="C29" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>117</v>
@@ -1272,15 +1380,15 @@
       <c r="C30" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="3" t="s">
         <v>119</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="3" t="s">
         <v>120</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -1289,145 +1397,151 @@
       <c r="C31" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>123</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="C32" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="4" t="s">
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="s">
+      <c r="B33" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="E33" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="s">
+      <c r="B34" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="D34" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="s">
+      <c r="B35" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="B36" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="s">
+      <c r="C36" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="D36" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="E36" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="B37" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="s">
+      <c r="C37" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="E37" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="s">
+      <c r="B38" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="3" t="s">
         <v>149</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="3" t="s">
         <v>150</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="3" t="s">
         <v>152</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -1436,22 +1550,181 @@
       <c r="C40" s="1" t="s">
         <v>155</v>
       </c>
+      <c r="D40" s="3" t="s">
+        <v>156</v>
+      </c>
       <c r="E40" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="s">
-        <v>150</v>
+      <c r="A41" s="3" t="s">
+        <v>157</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>157</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>157</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="198">
   <si>
     <t>word</t>
   </si>
@@ -125,6 +125,18 @@
   </si>
   <si>
     <t>بو آبداللق</t>
+  </si>
+  <si>
+    <t>آبدان</t>
+  </si>
+  <si>
+    <t>ковш, ведро, кувшин</t>
+  </si>
+  <si>
+    <t>abdan абдан</t>
+  </si>
+  <si>
+    <t>بو بالابان آبدان</t>
   </si>
   <si>
     <t>آبدست</t>
@@ -1061,7 +1073,7 @@
         <v>45</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -1078,7 +1090,7 @@
         <v>49</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -1092,10 +1104,10 @@
         <v>52</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -1109,24 +1121,24 @@
         <v>56</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>9</v>
@@ -1151,33 +1163,33 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>72</v>
@@ -1194,10 +1206,10 @@
         <v>75</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -1214,7 +1226,7 @@
         <v>80</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
@@ -1248,7 +1260,7 @@
         <v>88</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -1265,7 +1277,7 @@
         <v>92</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -1282,7 +1294,7 @@
         <v>96</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25">
@@ -1316,7 +1328,7 @@
         <v>104</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -1329,11 +1341,11 @@
       <c r="C27" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>108</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28">
@@ -1346,11 +1358,11 @@
       <c r="C28" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="4" t="s">
         <v>112</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29">
@@ -1364,7 +1376,7 @@
         <v>115</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>45</v>
+        <v>116</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>9</v>
@@ -1372,16 +1384,16 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>9</v>
@@ -1401,41 +1413,41 @@
         <v>123</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>128</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="34">
@@ -1452,7 +1464,7 @@
         <v>134</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35">
@@ -1466,24 +1478,24 @@
         <v>137</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>9</v>
@@ -1528,13 +1540,13 @@
         <v>150</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>58</v>
+        <v>151</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>9</v>
@@ -1542,10 +1554,10 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>154</v>
+        <v>62</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>155</v>
@@ -1568,7 +1580,7 @@
         <v>159</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>9</v>
@@ -1576,16 +1588,16 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>9</v>
@@ -1626,36 +1638,36 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D45" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1698,13 +1710,13 @@
         <v>188</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>9</v>
@@ -1712,19 +1724,36 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>193</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="210">
   <si>
     <t>word</t>
   </si>
@@ -139,6 +139,18 @@
     <t>بو بالابان آبدان</t>
   </si>
   <si>
+    <t>آبدار</t>
+  </si>
+  <si>
+    <t>сочный, питательный, свежий, красивый</t>
+  </si>
+  <si>
+    <t>abdar абдар</t>
+  </si>
+  <si>
+    <t>آبدار آب</t>
+  </si>
+  <si>
     <t>آبدست</t>
   </si>
   <si>
@@ -151,6 +163,18 @@
     <t>آبدست اتمک</t>
   </si>
   <si>
+    <t>آبه</t>
+  </si>
+  <si>
+    <t>эй!</t>
+  </si>
+  <si>
+    <t>abe абе</t>
+  </si>
+  <si>
+    <t>Междометие</t>
+  </si>
+  <si>
     <t>آچیق</t>
   </si>
   <si>
@@ -266,6 +290,18 @@
   </si>
   <si>
     <t>او ايشي</t>
+  </si>
+  <si>
+    <t>بالابان</t>
+  </si>
+  <si>
+    <t>большой</t>
+  </si>
+  <si>
+    <t>balaban балабан</t>
+  </si>
+  <si>
+    <t>او بالابان آدم</t>
   </si>
   <si>
     <t xml:space="preserve"> برکت</t>
@@ -1073,7 +1109,7 @@
         <v>45</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -1090,7 +1126,7 @@
         <v>49</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -1104,10 +1140,10 @@
         <v>52</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -1121,10 +1157,10 @@
         <v>56</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -1138,7 +1174,7 @@
         <v>60</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>9</v>
@@ -1146,33 +1182,33 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>9</v>
@@ -1180,19 +1216,19 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -1206,27 +1242,27 @@
         <v>75</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="21">
@@ -1240,10 +1276,10 @@
         <v>83</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -1260,7 +1296,7 @@
         <v>88</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>9</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23">
@@ -1277,7 +1313,7 @@
         <v>92</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1294,7 +1330,7 @@
         <v>96</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -1328,7 +1364,7 @@
         <v>104</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
@@ -1345,7 +1381,7 @@
         <v>108</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
@@ -1358,11 +1394,11 @@
       <c r="C28" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -1393,160 +1429,160 @@
         <v>119</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>9</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D31" s="3" t="s">
         <v>123</v>
       </c>
+      <c r="D31" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="E31" s="1" t="s">
-        <v>9</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>130</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>140</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>9</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>9</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>9</v>
@@ -1557,13 +1593,13 @@
         <v>154</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>62</v>
+        <v>155</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>9</v>
@@ -1571,16 +1607,16 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>9</v>
@@ -1588,16 +1624,16 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>9</v>
@@ -1605,16 +1641,16 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>9</v>
@@ -1622,16 +1658,16 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>9</v>
@@ -1639,35 +1675,35 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="E45" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D46" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1706,19 +1742,19 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1727,13 +1763,13 @@
         <v>192</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>9</v>
@@ -1741,19 +1777,70 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>76</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="214">
   <si>
     <t>word</t>
   </si>
@@ -464,6 +464,18 @@
   </si>
   <si>
     <t>بن سنی سویم</t>
+  </si>
+  <si>
+    <t>سیلگی</t>
+  </si>
+  <si>
+    <t>тряпка</t>
+  </si>
+  <si>
+    <t>silgi сильги</t>
+  </si>
+  <si>
+    <t>بو سیلگی</t>
   </si>
   <si>
     <t>صفت</t>
@@ -1582,7 +1594,7 @@
         <v>153</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>9</v>
@@ -1590,16 +1602,16 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>9</v>
@@ -1644,13 +1656,13 @@
         <v>166</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>70</v>
+        <v>167</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>9</v>
@@ -1658,10 +1670,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>171</v>
@@ -1684,7 +1696,7 @@
         <v>175</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>9</v>
@@ -1692,16 +1704,16 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>9</v>
@@ -1742,36 +1754,36 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D49" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D50" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1814,13 +1826,13 @@
         <v>204</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>9</v>
@@ -1828,18 +1840,35 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>209</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>84</v>
       </c>
     </row>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -103,6 +103,18 @@
     <t>بو آبانی</t>
   </si>
   <si>
+    <t>آبدار</t>
+  </si>
+  <si>
+    <t>сочный, питательный, свежий, красивый</t>
+  </si>
+  <si>
+    <t>abdar абдар</t>
+  </si>
+  <si>
+    <t>آبدار آب</t>
+  </si>
+  <si>
     <t>آبدال</t>
   </si>
   <si>
@@ -139,18 +151,6 @@
     <t>بو بالابان آبدان</t>
   </si>
   <si>
-    <t>آبدار</t>
-  </si>
-  <si>
-    <t>сочный, питательный, свежий, красивый</t>
-  </si>
-  <si>
-    <t>abdar абдар</t>
-  </si>
-  <si>
-    <t>آبدار آب</t>
-  </si>
-  <si>
     <t>آبدست</t>
   </si>
   <si>
@@ -304,7 +304,7 @@
     <t>او بالابان آدم</t>
   </si>
   <si>
-    <t xml:space="preserve"> برکت</t>
+    <t>برکت</t>
   </si>
   <si>
     <t>благословение</t>
@@ -1087,7 +1087,7 @@
         <v>37</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -1121,7 +1121,7 @@
         <v>45</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="237">
   <si>
     <t>word</t>
   </si>
@@ -163,6 +163,18 @@
     <t>آبدست اتمک</t>
   </si>
   <si>
+    <t>آبلا</t>
+  </si>
+  <si>
+    <t>старшая сестра</t>
+  </si>
+  <si>
+    <t>abla абла</t>
+  </si>
+  <si>
+    <t>بن آبلانی سویم</t>
+  </si>
+  <si>
     <t>آبه</t>
   </si>
   <si>
@@ -175,6 +187,18 @@
     <t>Междометие</t>
   </si>
   <si>
+    <t>آبیاری</t>
+  </si>
+  <si>
+    <t>помощь, подмога</t>
+  </si>
+  <si>
+    <t>abiyarı абияры</t>
+  </si>
+  <si>
+    <t>آبیاری اتمک</t>
+  </si>
+  <si>
     <t>آچیق</t>
   </si>
   <si>
@@ -268,6 +292,18 @@
     <t>Частица</t>
   </si>
   <si>
+    <t>اوقومق</t>
+  </si>
+  <si>
+    <t>читать</t>
+  </si>
+  <si>
+    <t>oqumaq</t>
+  </si>
+  <si>
+    <t>سن اوقویسڭمی؟</t>
+  </si>
+  <si>
     <t>اولر</t>
   </si>
   <si>
@@ -400,6 +436,15 @@
     <t>بیلگی نوری</t>
   </si>
   <si>
+    <t>بیوک</t>
+  </si>
+  <si>
+    <t>büyük буюк</t>
+  </si>
+  <si>
+    <t>بیوک کتاب</t>
+  </si>
+  <si>
     <t>پنجره</t>
   </si>
   <si>
@@ -499,6 +544,18 @@
     <t>بركتلی طوپراق</t>
   </si>
   <si>
+    <t>عابد</t>
+  </si>
+  <si>
+    <t>слуга, поклоняющийся</t>
+  </si>
+  <si>
+    <t>abit абит</t>
+  </si>
+  <si>
+    <t>بركتلی عابد</t>
+  </si>
+  <si>
     <t>عبا</t>
   </si>
   <si>
@@ -511,6 +568,18 @@
     <t>بو عبا</t>
   </si>
   <si>
+    <t>عبث</t>
+  </si>
+  <si>
+    <t>напрасный, бесполезный</t>
+  </si>
+  <si>
+    <t>abes абес</t>
+  </si>
+  <si>
+    <t>عبث فعل</t>
+  </si>
+  <si>
     <t>عبد</t>
   </si>
   <si>
@@ -598,7 +667,7 @@
     <t>kitap китап</t>
   </si>
   <si>
-    <t>بو کتاب</t>
+    <t>بن کتاب اوقویم</t>
   </si>
   <si>
     <t>لغت</t>
@@ -1152,10 +1221,10 @@
         <v>52</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -1169,10 +1238,10 @@
         <v>56</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -1203,10 +1272,10 @@
         <v>64</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -1220,7 +1289,7 @@
         <v>68</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>9</v>
@@ -1228,33 +1297,33 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>9</v>
@@ -1262,19 +1331,19 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -1288,27 +1357,27 @@
         <v>83</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>84</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="23">
@@ -1322,10 +1391,10 @@
         <v>91</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1342,7 +1411,7 @@
         <v>96</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25">
@@ -1359,7 +1428,7 @@
         <v>100</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>9</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26">
@@ -1376,7 +1445,7 @@
         <v>104</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -1393,7 +1462,7 @@
         <v>108</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -1427,7 +1496,7 @@
         <v>116</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -1444,7 +1513,7 @@
         <v>120</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31">
@@ -1457,11 +1526,11 @@
       <c r="C31" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>124</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
@@ -1492,78 +1561,78 @@
         <v>131</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>9</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D34" s="3" t="s">
         <v>135</v>
       </c>
+      <c r="D34" s="4" t="s">
+        <v>136</v>
+      </c>
       <c r="E34" s="1" t="s">
-        <v>9</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>142</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>146</v>
+        <v>65</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
@@ -1580,7 +1649,7 @@
         <v>150</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -1597,24 +1666,24 @@
         <v>154</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>9</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="41">
@@ -1631,7 +1700,7 @@
         <v>161</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>9</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42">
@@ -1648,7 +1717,7 @@
         <v>165</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43">
@@ -1673,13 +1742,13 @@
         <v>170</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>9</v>
@@ -1713,7 +1782,7 @@
         <v>179</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>9</v>
@@ -1721,16 +1790,16 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>9</v>
@@ -1738,52 +1807,52 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B50" s="2" t="s">
+      <c r="A50" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="B50" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1815,7 +1884,7 @@
         <v>202</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>9</v>
@@ -1823,16 +1892,16 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D53" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>9</v>
@@ -1840,10 +1909,10 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>205</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>209</v>
@@ -1866,10 +1935,112 @@
         <v>213</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>84</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -298,7 +298,7 @@
     <t>читать</t>
   </si>
   <si>
-    <t>oqumaq</t>
+    <t>oqumaq окъумакъ</t>
   </si>
   <si>
     <t>سن اوقویسڭمی؟</t>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="249">
   <si>
     <t>word</t>
   </si>
@@ -424,6 +424,18 @@
     <t>بو نه؟</t>
   </si>
   <si>
+    <t>بورا</t>
+  </si>
+  <si>
+    <t>это место</t>
+  </si>
+  <si>
+    <t>bura бура</t>
+  </si>
+  <si>
+    <t>بوراده</t>
+  </si>
+  <si>
     <t>بیلگی</t>
   </si>
   <si>
@@ -454,6 +466,18 @@
     <t>pencere пенджере</t>
   </si>
   <si>
+    <t>چوق</t>
+  </si>
+  <si>
+    <t>много</t>
+  </si>
+  <si>
+    <t>coq чокъ</t>
+  </si>
+  <si>
+    <t>بوگون هوا چوق گوزل</t>
+  </si>
+  <si>
     <t>ستان</t>
   </si>
   <si>
@@ -541,7 +565,7 @@
     <t>topraq топракъ</t>
   </si>
   <si>
-    <t>بركتلی طوپراق</t>
+    <t>برکتلی طوپراق</t>
   </si>
   <si>
     <t>عابد</t>
@@ -553,7 +577,7 @@
     <t>abit абит</t>
   </si>
   <si>
-    <t>بركتلی عابد</t>
+    <t>برکتلی عابد</t>
   </si>
   <si>
     <t>عبا</t>
@@ -670,6 +694,18 @@
     <t>بن کتاب اوقویم</t>
   </si>
   <si>
+    <t>کلمک</t>
+  </si>
+  <si>
+    <t>приходить, возвращаться</t>
+  </si>
+  <si>
+    <t>kelmek кельмек</t>
+  </si>
+  <si>
+    <t>کل بوراده</t>
+  </si>
+  <si>
     <t>لغت</t>
   </si>
   <si>
@@ -712,7 +748,7 @@
     <t>mekân мекян</t>
   </si>
   <si>
-    <t>مکانسز</t>
+    <t>بو مکان چوق گوزل</t>
   </si>
   <si>
     <t>يوق</t>
@@ -1598,7 +1634,7 @@
         <v>140</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>9</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36">
@@ -1606,47 +1642,47 @@
         <v>141</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>146</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>9</v>
@@ -1666,38 +1702,38 @@
         <v>154</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>157</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>88</v>
@@ -1705,19 +1741,19 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>163</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="E42" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="43">
@@ -1734,7 +1770,7 @@
         <v>169</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>9</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44">
@@ -1748,24 +1784,24 @@
         <v>172</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>9</v>
@@ -1773,16 +1809,16 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>9</v>
@@ -1819,7 +1855,7 @@
         <v>188</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
@@ -1844,30 +1880,30 @@
         <v>193</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>9</v>
@@ -1875,16 +1911,16 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>201</v>
+        <v>78</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>202</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>9</v>
@@ -1892,16 +1928,16 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>9</v>
@@ -1909,16 +1945,16 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>208</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>9</v>
@@ -1942,19 +1978,19 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D56" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1976,19 +2012,19 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2006,7 +2042,7 @@
         <v>230</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="60">
@@ -2014,13 +2050,13 @@
         <v>231</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>9</v>
@@ -2028,18 +2064,69 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E61" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>92</v>
       </c>
     </row>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="253">
   <si>
     <t>word</t>
   </si>
@@ -476,6 +476,18 @@
   </si>
   <si>
     <t>بوگون هوا چوق گوزل</t>
+  </si>
+  <si>
+    <t>حرف</t>
+  </si>
+  <si>
+    <t>буква</t>
+  </si>
+  <si>
+    <t>harif хариф</t>
+  </si>
+  <si>
+    <t>قریم تاتار حرفلری</t>
   </si>
   <si>
     <t>ستان</t>
@@ -1736,41 +1748,41 @@
         <v>162</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>165</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>167</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="E43" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="44">
@@ -1787,7 +1799,7 @@
         <v>173</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45">
@@ -1804,7 +1816,7 @@
         <v>177</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46">
@@ -1818,7 +1830,7 @@
         <v>180</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>9</v>
@@ -1826,16 +1838,16 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>9</v>
@@ -1889,7 +1901,7 @@
         <v>196</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
@@ -1906,7 +1918,7 @@
         <v>200</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
@@ -1914,13 +1926,13 @@
         <v>201</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>9</v>
@@ -1928,10 +1940,10 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>206</v>
@@ -1954,7 +1966,7 @@
         <v>210</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>9</v>
@@ -1962,16 +1974,16 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>9</v>
@@ -2012,37 +2024,37 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D58" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E58" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>73</v>
+      <c r="E59" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="60">
@@ -2059,7 +2071,7 @@
         <v>234</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61">
@@ -2101,13 +2113,13 @@
         <v>243</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>9</v>
@@ -2115,18 +2127,35 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E64" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>92</v>
       </c>
     </row>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="256">
   <si>
     <t>word</t>
   </si>
@@ -250,7 +250,7 @@
     <t>перс, чужестранец, иностранец</t>
   </si>
   <si>
-    <t>acemi аджеми</t>
+    <t>aʿcemi аʿджеми</t>
   </si>
   <si>
     <t>بو اعجمی</t>
@@ -586,7 +586,7 @@
     <t>слуга, поклоняющийся</t>
   </si>
   <si>
-    <t>abit абит</t>
+    <t>ʿabit ʿабит</t>
   </si>
   <si>
     <t>برکتلی عابد</t>
@@ -598,7 +598,7 @@
     <t>грубая шерстяная материя, пальто, риза</t>
   </si>
   <si>
-    <t>aba аба</t>
+    <t>ʿaba ʿаба</t>
   </si>
   <si>
     <t>بو عبا</t>
@@ -610,7 +610,7 @@
     <t>напрасный, бесполезный</t>
   </si>
   <si>
-    <t>abes абес</t>
+    <t>ʿabes ʿабес</t>
   </si>
   <si>
     <t>عبث فعل</t>
@@ -622,7 +622,7 @@
     <t>раб, слуга, создание, человек</t>
   </si>
   <si>
-    <t>abd абд</t>
+    <t>ʿabd ʿабд</t>
   </si>
   <si>
     <t>بو عبد</t>
@@ -631,7 +631,7 @@
     <t>عجم</t>
   </si>
   <si>
-    <t>acem аджем</t>
+    <t>ʿacem ʿаджем</t>
   </si>
   <si>
     <t>بو عجم</t>
@@ -643,7 +643,7 @@
     <t>Персия</t>
   </si>
   <si>
-    <t>acemistan аджемистан</t>
+    <t>ʿacemistan ʿаджемистан</t>
   </si>
   <si>
     <t>بو عجمستان</t>
@@ -655,7 +655,7 @@
     <t>действие, глагол</t>
   </si>
   <si>
-    <t>fiil фииль</t>
+    <t>fiʿil фиʿиль</t>
   </si>
   <si>
     <t>فیل</t>
@@ -770,6 +770,15 @@
   </si>
   <si>
     <t>yoq йокъ</t>
+  </si>
+  <si>
+    <t>الله</t>
+  </si>
+  <si>
+    <t>Аллах</t>
+  </si>
+  <si>
+    <t>Allah Аллагь</t>
   </si>
 </sst>
 </file>
@@ -2159,6 +2168,23 @@
         <v>92</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -256,6 +256,15 @@
     <t>بو اعجمی</t>
   </si>
   <si>
+    <t>الله</t>
+  </si>
+  <si>
+    <t>Аллах</t>
+  </si>
+  <si>
+    <t>Allah Аллагь</t>
+  </si>
+  <si>
     <t>او</t>
   </si>
   <si>
@@ -484,7 +493,7 @@
     <t>буква</t>
   </si>
   <si>
-    <t>harif хариф</t>
+    <t>harif хьариф (ариф)</t>
   </si>
   <si>
     <t>قریم تاتار حرفلری</t>
@@ -770,15 +779,6 @@
   </si>
   <si>
     <t>yoq йокъ</t>
-  </si>
-  <si>
-    <t>الله</t>
-  </si>
-  <si>
-    <t>Аллах</t>
-  </si>
-  <si>
-    <t>Allah Аллагь</t>
   </si>
 </sst>
 </file>
@@ -1414,7 +1414,7 @@
         <v>83</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>9</v>
@@ -1422,7 +1422,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>85</v>
@@ -1434,174 +1434,174 @@
         <v>87</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="D23" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="D24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="E26" s="1" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="E27" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="E28" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="E29" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="E30" s="1" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="D31" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="E31" s="1" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>9</v>
@@ -1609,78 +1609,78 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="E33" s="1" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="D34" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>136</v>
-      </c>
       <c r="E34" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="E35" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>146</v>
@@ -1689,7 +1689,7 @@
         <v>147</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
@@ -1697,16 +1697,16 @@
         <v>148</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="E38" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
@@ -1720,41 +1720,41 @@
         <v>153</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>154</v>
+        <v>65</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>9</v>
@@ -1762,101 +1762,101 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D42" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="E42" s="1" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>167</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>169</v>
+        <v>91</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="C44" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="E44" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="E45" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="D46" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="E46" s="1" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="D47" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>9</v>
@@ -1873,7 +1873,7 @@
         <v>187</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>9</v>
@@ -1881,16 +1881,16 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>9</v>
@@ -1898,16 +1898,16 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="D50" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>9</v>
@@ -1915,44 +1915,44 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="E51" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="E52" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>206</v>
@@ -1969,13 +1969,13 @@
         <v>208</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="D54" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>9</v>
@@ -1983,16 +1983,16 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>9</v>
@@ -2009,7 +2009,7 @@
         <v>217</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>9</v>
@@ -2017,16 +2017,16 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="D57" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>9</v>
@@ -2034,84 +2034,84 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="D58" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="E58" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="s">
+      <c r="B59" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="D59" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="E59" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="s">
+      <c r="B60" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="D60" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>73</v>
+      <c r="E60" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="D61" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="E61" s="1" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="D62" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>9</v>
@@ -2119,16 +2119,16 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="C63" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="D63" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>9</v>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>244</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>248</v>
@@ -2156,16 +2156,16 @@
         <v>250</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="D65" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="E65" s="1" t="s">
-        <v>92</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
@@ -2182,7 +2182,7 @@
         <v>253</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>9</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -250,7 +250,7 @@
     <t>перс, чужестранец, иностранец</t>
   </si>
   <si>
-    <t>aʿcemi аʿджеми</t>
+    <t>acemi аджеми</t>
   </si>
   <si>
     <t>بو اعجمی</t>
@@ -262,7 +262,7 @@
     <t>Аллах</t>
   </si>
   <si>
-    <t>Allah Аллагь</t>
+    <t>Allah Аллах</t>
   </si>
   <si>
     <t>او</t>
@@ -493,7 +493,7 @@
     <t>буква</t>
   </si>
   <si>
-    <t>harif хьариф (ариф)</t>
+    <t>harif хариф (ариф)</t>
   </si>
   <si>
     <t>قریم تاتار حرفلری</t>
@@ -595,7 +595,7 @@
     <t>слуга, поклоняющийся</t>
   </si>
   <si>
-    <t>ʿabit ʿабит</t>
+    <t>abit абит</t>
   </si>
   <si>
     <t>برکتلی عابد</t>
@@ -607,7 +607,7 @@
     <t>грубая шерстяная материя, пальто, риза</t>
   </si>
   <si>
-    <t>ʿaba ʿаба</t>
+    <t>aba аба</t>
   </si>
   <si>
     <t>بو عبا</t>
@@ -619,7 +619,7 @@
     <t>напрасный, бесполезный</t>
   </si>
   <si>
-    <t>ʿabes ʿабес</t>
+    <t>abes абес</t>
   </si>
   <si>
     <t>عبث فعل</t>
@@ -631,7 +631,7 @@
     <t>раб, слуга, создание, человек</t>
   </si>
   <si>
-    <t>ʿabd ʿабд</t>
+    <t>abd абд</t>
   </si>
   <si>
     <t>بو عبد</t>
@@ -640,7 +640,7 @@
     <t>عجم</t>
   </si>
   <si>
-    <t>ʿacem ʿаджем</t>
+    <t>acem аджем</t>
   </si>
   <si>
     <t>بو عجم</t>
@@ -652,7 +652,7 @@
     <t>Персия</t>
   </si>
   <si>
-    <t>ʿacemistan ʿаджемистан</t>
+    <t>acemistan аджемистан</t>
   </si>
   <si>
     <t>بو عجمستان</t>
@@ -664,7 +664,7 @@
     <t>действие, глагол</t>
   </si>
   <si>
-    <t>fiʿil фиʿиль</t>
+    <t>fiil фииль</t>
   </si>
   <si>
     <t>فیل</t>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="264">
   <si>
     <t>word</t>
   </si>
@@ -779,6 +779,30 @@
   </si>
   <si>
     <t>yoq йокъ</t>
+  </si>
+  <si>
+    <t>بخت</t>
+  </si>
+  <si>
+    <t>счастье</t>
+  </si>
+  <si>
+    <t>baht</t>
+  </si>
+  <si>
+    <t>بختلى</t>
+  </si>
+  <si>
+    <t>счастливый</t>
+  </si>
+  <si>
+    <t>bahıtlı</t>
+  </si>
+  <si>
+    <t>بختيار</t>
+  </si>
+  <si>
+    <t>bahtiyar</t>
   </si>
 </sst>
 </file>
@@ -2185,6 +2209,48 @@
         <v>95</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -349,6 +349,30 @@
     <t>او بالابان آدم</t>
   </si>
   <si>
+    <t>بخت</t>
+  </si>
+  <si>
+    <t>счастье</t>
+  </si>
+  <si>
+    <t>baht бахт</t>
+  </si>
+  <si>
+    <t>بختلى</t>
+  </si>
+  <si>
+    <t>счастливый</t>
+  </si>
+  <si>
+    <t>bahıtlı бахытлы</t>
+  </si>
+  <si>
+    <t>بختيار</t>
+  </si>
+  <si>
+    <t>bahtiyar бахтияр</t>
+  </si>
+  <si>
     <t>برکت</t>
   </si>
   <si>
@@ -779,30 +803,6 @@
   </si>
   <si>
     <t>yoq йокъ</t>
-  </si>
-  <si>
-    <t>بخت</t>
-  </si>
-  <si>
-    <t>счастье</t>
-  </si>
-  <si>
-    <t>baht</t>
-  </si>
-  <si>
-    <t>بختلى</t>
-  </si>
-  <si>
-    <t>счастливый</t>
-  </si>
-  <si>
-    <t>bahıtlı</t>
-  </si>
-  <si>
-    <t>بختيار</t>
-  </si>
-  <si>
-    <t>bahtiyar</t>
   </si>
 </sst>
 </file>
@@ -1573,25 +1573,19 @@
       <c r="C29" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="E29" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>14</v>
@@ -1599,33 +1593,30 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>9</v>
@@ -1633,33 +1624,33 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>91</v>
@@ -1667,135 +1658,135 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>135</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>147</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="D40" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="E41" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>165</v>
+        <v>65</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>9</v>
@@ -1803,19 +1794,19 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
@@ -1823,115 +1814,115 @@
         <v>166</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>168</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>172</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="E45" s="1" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="E46" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="E49" s="1" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>9</v>
@@ -1939,16 +1930,16 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>9</v>
@@ -1956,33 +1947,33 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>9</v>
@@ -1990,16 +1981,16 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>9</v>
@@ -2007,30 +1998,30 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="E55" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>215</v>
@@ -2041,16 +2032,16 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>221</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>9</v>
@@ -2058,16 +2049,16 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>9</v>
@@ -2075,118 +2066,118 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B60" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D60" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E60" s="2" t="s">
+      <c r="E60" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>73</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B63" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C63" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D63" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>247</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>9</v>
@@ -2194,30 +2185,33 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>253</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="D67" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>9</v>
@@ -2225,30 +2219,36 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="D68" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>260</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>263</v>
       </c>
+      <c r="D69" s="3" t="s">
+        <v>261</v>
+      </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
